--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李冠燃_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李冠燃_脚本与截图/软件测试测试用例.xlsx
@@ -11,7 +11,7 @@
     <sheet name="用例统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-001</t>
+          <t>TC-PD-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片删除</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>本地上传_jpg_2MB</t>
+          <t>删除_自己的图片</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01有图片</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=2MB_jpg</t>
+          <t>POST /picture/delete id=我的图片</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, url 字段为可访问图片链接</t>
+          <t>code=0, isDelete=1</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -603,7 +603,7 @@
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-002</t>
+          <t>TC-PD-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片删除</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -626,22 +626,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>本地上传_png</t>
+          <t>删除_别人的图片_越权</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_png</t>
+          <t>POST /picture/delete id=别人图片</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, picFormat=png</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-003</t>
+          <t>TC-PD-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片删除</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -679,22 +679,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>本地上传_超过2MB_应失败</t>
+          <t>删除_不存在的图片</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=5MB_jpg</t>
+          <t>POST /picture/delete id=999999</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-004</t>
+          <t>TC-PG-001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片查询</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -728,26 +728,26 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>本地上传_非图片_应失败</t>
+          <t>按id查询_正常</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>已有图片</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=test.pdf</t>
+          <t>GET /picture/get?id=1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -762,7 +762,7 @@
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-005</t>
+          <t>TC-PG-002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片查询</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -781,26 +781,26 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>本地上传_空文件_应失败</t>
+          <t>按id查询_不存在</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=0byte</t>
+          <t>GET /picture/get?id=999999</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-001</t>
+          <t>TC-PV-001</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片VO查询</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_有结果</t>
+          <t>查询VO_正常</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text='猫'</t>
+          <t>GET /picture/get/vo?id=1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>返回含'猫'的图片列表</t>
+          <t>code=0, PictureVO</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-002</t>
+          <t>TC-PV-002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片VO查询</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_无结果</t>
+          <t>查询VO_未登录</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text='xyz999'</t>
+          <t>GET /picture/get/vo?id=1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>返回空列表</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -921,7 +921,7 @@
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-003</t>
+          <t>TC-PE-001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片编辑</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -940,26 +940,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_空文本</t>
+          <t>编辑_名称正常</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01有图片</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text=''</t>
+          <t>POST /picture/edit id=1 name='新名'</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 或全部图片</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -974,7 +974,7 @@
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-004</t>
+          <t>TC-PE-002</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片编辑</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -993,26 +993,26 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_超长</t>
+          <t>编辑_越权</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1. text=1000字符</t>
+          <t>POST /picture/edit id=别人图片</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-005</t>
+          <t>TC-PE-003</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片编辑</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>关键字搜图_未登录</t>
+          <t>编辑_不存在</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture</t>
+          <t>POST /picture/edit id=999999</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-EB-001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1090,35 +1090,35 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片批量编辑</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>上传_20并发</t>
+          <t>批量编辑_正常</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>testuser01有多张</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 20 线程上传 2MB jpg</t>
+          <t>POST /picture/edit/batch ids=[1,2,3] category='风景'</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 3s, 错误率 &lt; 5%</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-EB-002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1143,35 +1143,35 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片批量编辑</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>上传_缺multipart边界</t>
+          <t>批量编辑_越权</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1. 发送不完整 multipart 请求</t>
+          <t>POST /picture/edit/batch ids=[别人图片]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>返回 400 或 415</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-PU-001</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片更新</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -1209,22 +1209,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>上传_伪PHP木马</t>
+          <t>更新_正常</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1. file=1.jpg 内容为 &lt;?php system($_GET['c']);?&gt;</t>
+          <t>POST /picture/update id=1 name='更新名'</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-006</t>
+          <t>TC-PU-002</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片更新</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1258,26 +1258,26 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>上传_bmp格式</t>
+          <t>更新_普通用户越权</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_bmp</t>
+          <t>POST /picture/update</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=bmp</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-007</t>
+          <t>TC-PL-001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片分页</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1311,26 +1311,26 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>上传_gif格式</t>
+          <t>分页查询_默认</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_gif</t>
+          <t>POST /picture/list/page current=1 pageSize=10</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=gif</t>
+          <t>code=0, records</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1345,7 +1345,7 @@
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-008</t>
+          <t>TC-PL-002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片分页</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1364,26 +1364,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>上传_webp格式</t>
+          <t>分页查询_普通用户</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_webp</t>
+          <t>POST /picture/list/page</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=webp</t>
+          <t>code=40100或code=0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-009</t>
+          <t>TC-PL-003</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片分页</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1417,26 +1417,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>上传_文件名含中文</t>
+          <t>分页查询_空页</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=中文图片.jpg</t>
+          <t>current=9999 pageSize=10</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 url 正确编码</t>
+          <t>code=0, records=[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-010</t>
+          <t>TC-LV-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/图片VO分页</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1470,26 +1470,26 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>上传_文件名含特殊字符</t>
+          <t>VO分页_正常</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file='im$g.jpg'</t>
+          <t>POST /picture/list/page/vo</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 url 已转义</t>
+          <t>code=0, PictureVO列表</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-006</t>
+          <t>TC-LV-002</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片VO分页</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1527,22 +1527,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>搜图_精确匹配</t>
+          <t>VO分页_普通用户</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/search/picture text='StarPicture'</t>
+          <t>POST /picture/list/page/vo</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含结果</t>
+          <t>code=40100或code=0</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1557,7 +1557,7 @@
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-007</t>
+          <t>TC-VC-001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1567,35 +1567,35 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片缓存分页</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>搜图_缺text字段</t>
+          <t>缓存分页_正常</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1. body 为空</t>
+          <t>POST /picture/list/page/vo/cache</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0, 含缓存</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-008</t>
+          <t>TC-TG-001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片标签分类</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
@@ -1633,22 +1633,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>搜图_SQL注入</t>
+          <t>获取标签分类</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>已有图片</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1. text="' OR 1=1 --"</t>
+          <t>GET /picture/tag_category</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 拒绝注入</t>
+          <t>code=0, tags+categories</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-009</t>
+          <t>TC-RV-001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片审核</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>搜图_XSS注入</t>
+          <t>审核_通过</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin,待审核图片</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1. text="&lt;script&gt;alert(1)&lt;/script&gt;"</t>
+          <t>POST /picture/review id=1 reviewStatus=1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 渲染时被转义</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-PX-010</t>
+          <t>TC-RV-002</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/图片审核</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1735,26 +1735,26 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>搜图_含Unicode字符</t>
+          <t>审核_拒绝</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1. text='测试中文搜索'</t>
+          <t>POST /picture/review id=1 reviewStatus=2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-001</t>
+          <t>TC-RV-003</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>/图片管理</t>
+          <t>/图片审核</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1792,22 +1792,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>按id查询图片</t>
+          <t>审核_普通用户越权</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1. GET /picture/get/vo?id=1</t>
+          <t>POST /picture/review</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含完整图片信息</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
     <row r="26" ht="80" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-002</t>
+          <t>TC-UR-001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>/图片管理</t>
+          <t>/URL上传</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1845,22 +1845,22 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>分页查询所有图片</t>
+          <t>URL上传_正常</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1. POST /picture/list/page/vo current=1 pageSize=10</t>
+          <t>POST /picture/upload/url fileUrl='https://example.com/1.jpg'</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 records含图片列表</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-003</t>
+          <t>TC-UR-002</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1885,35 +1885,35 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>/图片管理</t>
+          <t>/URL上传</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>查询_id类型错误</t>
+          <t>URL上传_内网IP_拒绝</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1. GET /picture/get/vo?id='abc'</t>
+          <t>fileUrl='http://127.0.0.1/x.jpg'</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-UR-003</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1938,35 +1938,35 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>/图片搜索</t>
+          <t>/URL上传</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>搜图_50并发</t>
+          <t>URL上传_404</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程 POST /picture/search/picture</t>
+          <t>fileUrl='https://example.com/404.jpg'</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 500ms, 错误率 &lt; 1%</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-URL-001</t>
+          <t>TC-UB-001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>/图片上传</t>
+          <t>/批量上传</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -2004,22 +2004,22 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>URL上传_内网IP</t>
+          <t>批量上传_5张</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1. fileUrl='http://127.0.0.1/x.jpg'</t>
+          <t>POST /picture/upload/batch files=[5张jpg]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 拒绝内网</t>
+          <t>code=0, 5条记录</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2031,8 +2031,909 @@
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-UB-002</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>/批量上传</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>批量上传_超20张</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>POST /picture/upload/batch files=[30张]</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TC-SP-001</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>/关键字搜图</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>搜图_正常</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>已有图片</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>POST /picture/search/picture text='猫'</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>code=0, 结果列表</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TC-SP-002</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>/关键字搜图</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>搜图_无结果</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>text='xyz999'</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>code=0, []</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TC-SP-003</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>/关键字搜图</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>搜图_SQL注入</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>text="' OR 1=1 --"</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TC-SC-001</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/颜色搜图</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>搜图_蓝色</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>已有图片</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>POST /picture/search/color picColor='#0000FF'</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>code=0</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TC-SC-002</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/颜色搜图</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>搜图_无效颜色</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>picColor='notacolor'</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TC-OC-001</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>/AI扩图</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>创建扩图任务</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>testuser01有图片</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>POST /picture/out_painting/create_task pictureId=1</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>code=0, taskId</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TC-OC-002</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/AI扩图</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>任务_未登录</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>POST /picture/out_painting/create_task</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>code=40100</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TC-OG-001</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/AI扩图查询</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>查询任务状态</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>已创建任务</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>GET /picture/out_painting/get_task?taskId=xxx</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>code=0, status</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TC-PE-001</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/编辑代理</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>代理_正常URL</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>GET /picture/proxy/editor?url=https://example.com/1.jpg</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>返回图片</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TC-PE-002</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/编辑代理</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>代理_内网URL_拒绝</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>url='http://192.168.1.1/admin'</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-001</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>/图片上传</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>上传_20并发</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>20线程 POST /file/upload</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;3s</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="80" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TC-PERF-002</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>/图片分页</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>分页查询_50并发</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>JMeter</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>50线程 POST /picture/list/page</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>P95&lt;300ms</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-001</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>/图片上传</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>接口测试</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>上传_缺multipart边界</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>不完整multipart</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>400/415</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="80" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-001</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>/图片上传</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>上传_伪PHP木马</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>file=1.jpg内容为&lt;?php...?&gt;</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="80" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-002</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>/URL上传</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>URL上传_file协议</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>fileUrl='file:///etc/passwd'</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="80" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-003</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>/图片编辑</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>编辑_name注入XSS</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>name='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>code=0, 转义</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>李冠燃</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M29"/>
+  <autoFilter ref="A1:M46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2069,7 +2970,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -2079,27 +2980,27 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2109,7 +3010,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李冠燃_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李冠燃_脚本与截图/软件测试测试用例.xlsx
@@ -8,11 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="用例统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$46</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,14 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -50,7 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,39 +54,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,22 +439,22 @@
   <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>用例编号</t>
@@ -547,48 +521,49 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-PD-001</t>
+          <t>TC-PU-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>/图片删除</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>删除_自己的图片</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_jpg_2MB</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>testuser01有图片</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/delete id=我的图片</t>
+          <t>POST /file/upload
+Body: multipart file=2MB_jpg</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>code=0, isDelete=1</t>
+          <t>code=0, url 字段为可访问链接</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -600,48 +575,49 @@
       </c>
       <c r="M2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TC-PD-002</t>
+          <t>TC-PU-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>/图片删除</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>删除_别人的图片_越权</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_png</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>testuser02</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/delete id=别人图片</t>
+          <t>POST /file/upload
+Body: multipart file=1MB_png</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=0, picFormat=png</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -653,43 +629,44 @@
       </c>
       <c r="M3" s="2" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC-PD-003</t>
+          <t>TC-PU-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>/图片删除</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>删除_不存在的图片</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_超过2MB</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/delete id=999999</t>
+          <t>POST /file/upload
+Body: multipart file=5MB_jpg</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -706,48 +683,49 @@
       </c>
       <c r="M4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-001</t>
+          <t>TC-PU-004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>/图片查询</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>按id查询_正常</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_非图片文件</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>GET /picture/get?id=1</t>
+          <t>POST /file/upload
+Body: multipart file=test.pdf</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -759,43 +737,44 @@
       </c>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-PG-002</t>
+          <t>TC-PU-005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>/图片查询</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>按id查询_不存在</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_空文件</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>GET /picture/get?id=999999</t>
+          <t>POST /file/upload
+Body: multipart file=0byte.jpg</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -812,48 +791,49 @@
       </c>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-PV-001</t>
+          <t>TC-PUU-001</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>/图片VO查询</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload/url</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>查询VO_正常</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>URL上传_合法URL</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>GET /picture/get/vo?id=1</t>
+          <t>POST /picture/upload/url
+Body: {"fileUrl":"https://example.com/1.jpg","picName":"test"}</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>code=0, PictureVO</t>
+          <t>code=0, picture.url 已写入</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -865,48 +845,49 @@
       </c>
       <c r="M7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-PV-002</t>
+          <t>TC-PUU-002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>/图片VO查询</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload/url</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>查询VO_未登录</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>URL上传_内网URL_SSRF</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>GET /picture/get/vo?id=1</t>
+          <t>POST /picture/upload/url
+Body: {"fileUrl":"http://127.0.0.1/x.jpg"}</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>code=40100</t>
+          <t>code=40001, 防止 SSRF</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -918,48 +899,49 @@
       </c>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-PE-001</t>
+          <t>TC-PUU-003</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>/图片编辑</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>编辑_名称正常</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload/url</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>URL上传_404</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>testuser01有图片</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/edit id=1 name='新名'</t>
+          <t>POST /picture/upload/url
+Body: {"fileUrl":"https://example.com/notfound.jpg"}</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -971,48 +953,49 @@
       </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
-    <row r="10" ht="80" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-PE-002</t>
+          <t>TC-PUU-004</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>/图片编辑</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>编辑_越权</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload/url</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>URL上传_非图片URL</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>testuser02</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/edit id=别人图片</t>
+          <t>POST /picture/upload/url
+Body: {"fileUrl":"https://example.com/index.html"}</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1024,48 +1007,49 @@
       </c>
       <c r="M10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-PE-003</t>
+          <t>TC-PUB-001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>/图片编辑</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload/batch</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>编辑_不存在</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>批量上传_5张</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/edit id=999999</t>
+          <t>POST /picture/upload/batch
+Body: multipart files=[5张jpg]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=0, 5 条记录</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1077,48 +1061,49 @@
       </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-EB-001</t>
+          <t>TC-PUB-002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>/图片批量编辑</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>批量编辑_正常</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload/batch</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>批量上传_超过20张</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>testuser01有多张</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/edit/batch ids=[1,2,3] category='风景'</t>
+          <t>POST /picture/upload/batch
+Body: multipart files=[30张]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001 或只保存前N张</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1130,48 +1115,48 @@
       </c>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="80" customHeight="1">
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-EB-002</t>
+          <t>TC-PG-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>/图片批量编辑</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>/picture/get</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>批量编辑_越权</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>按id查询原数据</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>testuser02</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/edit/batch ids=[别人图片]</t>
+          <t>GET /picture/get?id=1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=0, 含完整 url</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1183,48 +1168,48 @@
       </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
-    <row r="14" ht="80" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-001</t>
+          <t>TC-PG-002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>/图片更新</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>更新_正常</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>/picture/get</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>查询_不存在id</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/update id=1 name='更新名'</t>
+          <t>GET /picture/get?id=999999</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1236,48 +1221,48 @@
       </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="80" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-PU-002</t>
+          <t>TC-PGV-001</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>/图片更新</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>/picture/get/vo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>更新_普通用户越权</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>按id查询VO</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/update</t>
+          <t>GET /picture/get/vo?id=1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=0, PictureVO</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1289,48 +1274,49 @@
       </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
-    <row r="16" ht="80" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-PL-001</t>
+          <t>TC-PLP-001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>/图片分页</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>/picture/list/page</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>分页查询_默认</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/list/page current=1 pageSize=10</t>
+          <t>POST /picture/list/page
+Body: {"current":1,"pageSize":10}</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>code=0, records</t>
+          <t>code=0, 10 条记录</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1342,48 +1328,49 @@
       </c>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="80" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-PL-002</t>
+          <t>TC-PLP-002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>/图片分页</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>分页查询_普通用户</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>/picture/list/page</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>分页_超大pageSize</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/list/page</t>
+          <t>POST /picture/list/page
+Body: {"current":1,"pageSize":10000}</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>code=40100或code=0</t>
+          <t>被限制或code=40001</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1395,48 +1382,49 @@
       </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
-    <row r="18" ht="80" customHeight="1">
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-PL-003</t>
+          <t>TC-PLP-003</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>/图片分页</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>分页查询_空页</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>/picture/list/page</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>分页_按标签过滤</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>current=9999 pageSize=10</t>
+          <t>POST /picture/list/page
+Body: {"tags":["tag1"]}</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>code=0, records=[]</t>
+          <t>返回含 tag1 的图片</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1448,48 +1436,49 @@
       </c>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="80" customHeight="1">
+    <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-LV-001</t>
+          <t>TC-PLPV-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>/图片VO分页</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>/picture/list/page/vo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>VO分页_正常</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>分页查询VO_管理员查所有</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/list/page/vo</t>
+          <t>POST /picture/list/page/vo
+Body: {"current":1,"pageSize":10}</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>code=0, PictureVO列表</t>
+          <t>返回所有用户图片</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1501,48 +1490,49 @@
       </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
-    <row r="20" ht="80" customHeight="1">
+    <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-LV-002</t>
+          <t>TC-PLC-001</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>/图片VO分页</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>/picture/list/page/vo/cache</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>VO分页_普通用户</t>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>缓存分页查询</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/list/page/vo</t>
+          <t>POST /picture/list/page/vo/cache
+Body: {"current":1,"pageSize":10}</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>code=40100或code=0</t>
+          <t>code=0, 第二次更快</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1554,48 +1544,49 @@
       </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
-    <row r="21" ht="80" customHeight="1">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-VC-001</t>
+          <t>TC-PD-001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>/图片缓存分页</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>/picture/delete</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>缓存分页_正常</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>删除自己的图片</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/list/page/vo/cache</t>
+          <t>POST /picture/delete
+Body: {"id":1}</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>code=0, 含缓存</t>
+          <t>code=0, isDelete=1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1607,48 +1598,49 @@
       </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="80" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-TG-001</t>
+          <t>TC-PD-002</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>/图片标签分类</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>/picture/delete</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>获取标签分类</t>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>删除别人的图片_越权</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>testuser02 Cookie</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>GET /picture/tag_category</t>
+          <t>POST /picture/delete
+Body: {"id":1}</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>code=0, tags+categories</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1660,43 +1652,44 @@
       </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
-    <row r="23" ht="80" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-RV-001</t>
+          <t>TC-PD-003</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>/图片审核</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>/picture/delete</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>审核_通过</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>管理员删任意图片</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>admin,待审核图片</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/review id=1 reviewStatus=1</t>
+          <t>POST /picture/delete
+Body: {"id":2}</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1713,43 +1706,44 @@
       </c>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
-    <row r="24" ht="80" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-RV-002</t>
+          <t>TC-PE-001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>/图片审核</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>/picture/edit</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>审核_拒绝</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>编辑名称简介标签</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/review id=1 reviewStatus=2</t>
+          <t>POST /picture/edit
+Body: {"id":1,"name":"新名","introduction":"新简介","tags":"[\"tag1\"]"}</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1766,48 +1760,49 @@
       </c>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="80" customHeight="1">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-RV-003</t>
+          <t>TC-PE-002</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>/图片审核</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>/picture/edit</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>审核_普通用户越权</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>编辑_XSS标签</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/review</t>
+          <t>POST /picture/edit
+Body: {"id":1,"tags":"[\"&lt;script&gt;alert(1)&lt;/script&gt;\"]"}</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=0, 渲染时被转义</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1819,48 +1814,49 @@
       </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
-    <row r="26" ht="80" customHeight="1">
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-001</t>
+          <t>TC-PE-003</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>/URL上传</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>URL上传_正常</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>/picture/edit</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>编辑_不存在的id</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/upload/url fileUrl='https://example.com/1.jpg'</t>
+          <t>POST /picture/edit
+Body: {"id":999999,"name":"x"}</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1872,48 +1868,49 @@
       </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="80" customHeight="1">
+    <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-002</t>
+          <t>TC-PEB-001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>/URL上传</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>/picture/edit/batch</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>URL上传_内网IP_拒绝</t>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>批量编辑_3张分类</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>fileUrl='http://127.0.0.1/x.jpg'</t>
+          <t>POST /picture/edit/batch
+Body: {"ids":[1,2,3],"category":"风景"}</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=0, 3张图category被更新</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -1925,43 +1922,44 @@
       </c>
       <c r="M27" s="2" t="inlineStr"/>
     </row>
-    <row r="28" ht="80" customHeight="1">
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-003</t>
+          <t>TC-PEB-002</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>/URL上传</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>URL上传_404</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>/picture/edit/batch</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>批量编辑_空数组</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>fileUrl='https://example.com/404.jpg'</t>
+          <t>POST /picture/edit/batch
+Body: {"ids":[]}</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1978,48 +1976,49 @@
       </c>
       <c r="M28" s="2" t="inlineStr"/>
     </row>
-    <row r="29" ht="80" customHeight="1">
+    <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-UB-001</t>
+          <t>TC-PUd-001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>/批量上传</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>/picture/update</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>批量上传_5张</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>管理员更新图片</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/upload/batch files=[5张jpg]</t>
+          <t>POST /picture/update
+Body: {"id":1,"name":"管理员修改"}</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>code=0, 5条记录</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2031,48 +2030,49 @@
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
-    <row r="30" ht="80" customHeight="1">
+    <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-UB-002</t>
+          <t>TC-PUd-002</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>/批量上传</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>/picture/update</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>批量上传_超20张</t>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>更新_非管理员越权</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/upload/batch files=[30张]</t>
+          <t>POST /picture/update
+Body: {"id":1}</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2084,48 +2084,48 @@
       </c>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="80" customHeight="1">
+    <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-001</t>
+          <t>TC-PTC-001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>/关键字搜图</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>/picture/tag_category</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>搜图_正常</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>获取标签分类聚合</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/search/picture text='猫'</t>
+          <t>GET /picture/tag_category</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>code=0, 结果列表</t>
+          <t>返回 tagList + categoryList</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2137,48 +2137,49 @@
       </c>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
-    <row r="32" ht="80" customHeight="1">
+    <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-002</t>
+          <t>TC-PR-001</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>/关键字搜图</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>/picture/review</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>搜图_无结果</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>管理员审核通过</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>text='xyz999'</t>
+          <t>POST /picture/review
+Body: {"id":1,"reviewStatus":1,"reviewMessage":"ok"}</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>code=0, []</t>
+          <t>code=0, reviewStatus=1</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2190,48 +2191,49 @@
       </c>
       <c r="M32" s="2" t="inlineStr"/>
     </row>
-    <row r="33" ht="80" customHeight="1">
+    <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TC-SP-003</t>
+          <t>TC-PR-002</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>/关键字搜图</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>/picture/review</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>搜图_SQL注入</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>管理员审核拒绝</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>text="' OR 1=1 --"</t>
+          <t>POST /picture/review
+Body: {"id":1,"reviewStatus":2,"reviewMessage":"违规"}</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=0, reviewStatus=2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -2243,48 +2245,49 @@
       </c>
       <c r="M33" s="2" t="inlineStr"/>
     </row>
-    <row r="34" ht="80" customHeight="1">
+    <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-SC-001</t>
+          <t>TC-PR-003</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>/颜色搜图</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>/picture/review</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>搜图_蓝色</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>审核_普通用户越权</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>已有图片</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/search/color picColor='#0000FF'</t>
+          <t>POST /picture/review
+Body: {"id":1}</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2296,48 +2299,49 @@
       </c>
       <c r="M34" s="2" t="inlineStr"/>
     </row>
-    <row r="35" ht="80" customHeight="1">
+    <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TC-SC-002</t>
+          <t>TC-PSP-001</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>/颜色搜图</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>/picture/search/picture</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>搜图_无效颜色</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>关键字搜图</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>picColor='notacolor'</t>
+          <t>POST /picture/search/picture
+Body: {"text":"猫"}</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>返回含'猫'的图片列表</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -2349,48 +2353,49 @@
       </c>
       <c r="M35" s="2" t="inlineStr"/>
     </row>
-    <row r="36" ht="80" customHeight="1">
+    <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-OC-001</t>
+          <t>TC-PSP-002</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>/AI扩图</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>创建扩图任务</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>/picture/search/picture</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>搜图_无结果</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>testuser01有图片</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/out_painting/create_task pictureId=1</t>
+          <t>POST /picture/search/picture
+Body: {"text":"xyz999"}</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>code=0, taskId</t>
+          <t>返回空列表</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2402,48 +2407,49 @@
       </c>
       <c r="M36" s="2" t="inlineStr"/>
     </row>
-    <row r="37" ht="80" customHeight="1">
+    <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TC-OC-002</t>
+          <t>TC-PSP-003</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>/AI扩图</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>任务_未登录</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>/picture/search/picture</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>搜图_空文本</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>POST /picture/out_painting/create_task</t>
+          <t>POST /picture/search/picture
+Body: {"text":""}</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>code=40100</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -2455,48 +2461,49 @@
       </c>
       <c r="M37" s="2" t="inlineStr"/>
     </row>
-    <row r="38" ht="80" customHeight="1">
+    <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-OG-001</t>
+          <t>TC-PSC-001</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>/AI扩图查询</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>/picture/search/color</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>查询任务状态</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>颜色搜图_蓝色</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>已创建任务</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>GET /picture/out_painting/get_task?taskId=xxx</t>
+          <t>POST /picture/search/color
+Body: {"picColor":"#0000FF"}</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>code=0, status</t>
+          <t>返回主色为蓝的图片</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2508,48 +2515,49 @@
       </c>
       <c r="M38" s="2" t="inlineStr"/>
     </row>
-    <row r="39" ht="80" customHeight="1">
+    <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TC-PE-001</t>
+          <t>TC-PSC-002</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>/编辑代理</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>代理_正常URL</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>/picture/search/color</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>颜色搜图_无效颜色值</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>GET /picture/proxy/editor?url=https://example.com/1.jpg</t>
+          <t>POST /picture/search/color
+Body: {"picColor":"notacolor"}</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>返回图片</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -2561,48 +2569,49 @@
       </c>
       <c r="M39" s="2" t="inlineStr"/>
     </row>
-    <row r="40" ht="80" customHeight="1">
+    <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-PE-002</t>
+          <t>TC-POP-001</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>/编辑代理</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>/picture/out_painting/create_task</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>代理_内网URL_拒绝</t>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>AI扩图_创建任务</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>url='http://192.168.1.1/admin'</t>
+          <t>POST /picture/out_painting/create_task
+Body: {"pictureId":1}</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=0, outputTaskId 非空</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -2614,48 +2623,48 @@
       </c>
       <c r="M40" s="2" t="inlineStr"/>
     </row>
-    <row r="41" ht="80" customHeight="1">
+    <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-POG-001</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>/图片上传</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>上传_20并发</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>/picture/out_painting/get_task</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>AI扩图_查询任务</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>JMeter</t>
+          <t>有任务</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20线程 POST /file/upload</t>
+          <t>GET /picture/out_painting/get_task?taskId=xxx</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>P95&lt;3s</t>
+          <t>返回任务状态</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -2667,48 +2676,48 @@
       </c>
       <c r="M41" s="2" t="inlineStr"/>
     </row>
-    <row r="42" ht="80" customHeight="1">
+    <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-PPE-001</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>/图片分页</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>分页查询_50并发</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>/picture/proxy/editor</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>编辑代理_跨域URL</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>JMeter</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>50线程 POST /picture/list/page</t>
+          <t>GET /picture/proxy/editor?url=https://example.com/1.jpg</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>P95&lt;300ms</t>
+          <t>返回图片二进制流</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -2720,48 +2729,48 @@
       </c>
       <c r="M42" s="2" t="inlineStr"/>
     </row>
-    <row r="43" ht="80" customHeight="1">
+    <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-PPE-002</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>/图片上传</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>上传_缺multipart边界</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>/picture/proxy/editor</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>编辑代理_内网URL_SSRF</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>不完整multipart</t>
+          <t>GET /picture/proxy/editor?url=http://192.168.1.1/admin</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>400/415</t>
+          <t>code=40001 拒绝内网</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -2773,48 +2782,49 @@
       </c>
       <c r="M43" s="2" t="inlineStr"/>
     </row>
-    <row r="44" ht="80" customHeight="1">
+    <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>/图片上传</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>上传_伪PHP木马</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>上传_20并发</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>file=1.jpg内容为&lt;?php...?&gt;</t>
+          <t>POST /file/upload 20线程 5s内启动
+Body: multipart file=2MB_jpg</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>P95 &lt; 3s, 错误率 &lt; 5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2826,48 +2836,50 @@
       </c>
       <c r="M44" s="2" t="inlineStr"/>
     </row>
-    <row r="45" ht="80" customHeight="1">
+    <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-002</t>
+          <t>TC-API-001</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>/URL上传</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>URL上传_file协议</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>/picture/upload</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>上传_缺multipart边界</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>fileUrl='file:///etc/passwd'</t>
+          <t>POST /file/upload
+Header: Content-Type: multipart/form-data (缺 boundary)
+Body: raw 乱码</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>400 或 415</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -2879,48 +2891,49 @@
       </c>
       <c r="M45" s="2" t="inlineStr"/>
     </row>
-    <row r="46" ht="80" customHeight="1">
+    <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-003</t>
+          <t>TC-API-002</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>/图片编辑</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>编辑_name注入XSS</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>/picture/edit</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>编辑_id类型错误</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>name='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+          <t>POST /picture/edit
+Body: {"id":"abc","name":"x"}</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>code=0, 转义</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -2931,87 +2944,6 @@
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M46"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>测试类型</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>用例数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>45</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李冠燃_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/李冠燃_脚本与截图/软件测试测试用例.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload/url</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload/url</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload/url</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload/url</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload/batch</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload/batch</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>/picture/get</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>/picture/get</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>/picture/get/vo</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>/picture/list/page</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>/picture/list/page</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>/picture/list/page</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>/picture/list/page/vo</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>/picture/list/page/vo/cache</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>/picture/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>/picture/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>/picture/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>/picture/edit</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>/picture/edit</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>/picture/edit</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>/picture/edit/batch</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>/picture/edit/batch</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>/picture/update</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>/picture/update</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>/picture/tag_category</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>/picture/review</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>/picture/review</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>/picture/review</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>/picture/search/picture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>/picture/search/picture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>/picture/search/picture</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>/picture/search/color</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>/picture/search/color</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>/picture/out_painting/create_task</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>/picture/out_painting/get_task</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>/picture/proxy/editor</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>/picture/proxy/editor</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>/picture/upload</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>/picture/edit</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
